--- a/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
+++ b/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>Biofuel</t>
+  </si>
   <si>
     <t>Energy Storage</t>
   </si>
@@ -23,6 +26,12 @@
   </si>
   <si>
     <t>Solar</t>
+  </si>
+  <si>
+    <t>Waste Gas</t>
+  </si>
+  <si>
+    <t>Wind</t>
   </si>
   <si>
     <t>Open year</t>
@@ -143,7 +152,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Energy Storage</c:v>
+                  <c:v>Biofuel</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -158,50 +167,83 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="13">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="21">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="24">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,19 +251,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2</c:v>
-                </c:pt>
+                <c:ptCount val="25"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -235,7 +268,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Natural Gas/Propane</c:v>
+                  <c:v>Energy Storage</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -250,50 +283,83 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="13">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="21">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="24">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -301,12 +367,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
-                <c:pt idx="4">
+                <c:ptCount val="25"/>
+                <c:pt idx="22">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -321,7 +393,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Solar</c:v>
+                  <c:v>Natural Gas/Propane</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -336,50 +408,83 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="25"/>
                 <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>2007</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2010</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2012</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="13">
                   <c:v>2013</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="16">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="17">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="18">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="19">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="20">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="21">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="22">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="23">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="24">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -387,52 +492,403 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="25"/>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>Solar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D62728"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>2001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>2004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>2005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Waste Gas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9467BD"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
                 <c:pt idx="8">
-                  <c:v>8</c:v>
+                  <c:v>2008</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13</c:v>
+                  <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>17</c:v>
+                  <c:v>2011</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>33</c:v>
+                  <c:v>2012</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>33</c:v>
-                </c:pt>
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Wind</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8C564B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -524,13 +980,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -840,18 +1296,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -862,128 +1321,192 @@
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="3">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="3">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="3">
         <v>2007</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3">
+    <row r="10" spans="1:7">
+      <c r="A10" s="3">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="3">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="3">
         <v>2010</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E12" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3">
+    <row r="13" spans="1:7">
+      <c r="A13" s="3">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="3">
         <v>2012</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E14" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3">
+    <row r="15" spans="1:7">
+      <c r="A15" s="3">
         <v>2013</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E15" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3">
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
         <v>2015</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E17" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3">
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
         <v>2016</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E18" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3">
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
         <v>2017</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E19" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3">
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
         <v>2018</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E20" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3">
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
         <v>2019</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E21" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3">
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
         <v>2020</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E22" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3">
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
         <v>2021</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E23" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3">
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
         <v>2022</v>
       </c>
-      <c r="B13" s="2">
+      <c r="C24" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E24" s="2">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3">
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
         <v>2023</v>
       </c>
-      <c r="B14" s="2">
+      <c r="C25" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E25" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3">
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
         <v>2024</v>
       </c>
-      <c r="B15" s="2">
+      <c r="C26" s="2">
         <v>2</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E26" s="2">
         <v>33</v>
       </c>
     </row>

--- a/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
+++ b/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -245,16 +245,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -283,10 +286,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -361,16 +364,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$26</c:f>
+              <c:f>Sheet1!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="22">
                   <c:v>1</c:v>
                 </c:pt>
@@ -378,6 +384,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -408,10 +417,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -486,16 +495,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$26</c:f>
+              <c:f>Sheet1!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
@@ -527,10 +539,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -605,16 +617,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$26</c:f>
+              <c:f>Sheet1!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
@@ -656,6 +671,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -685,10 +703,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -763,16 +781,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$26</c:f>
+              <c:f>Sheet1!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -801,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -879,16 +900,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$26</c:f>
+              <c:f>Sheet1!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1296,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1510,6 +1534,17 @@
         <v>33</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
+++ b/output_data/charts/facilities-Dublin-M100000US3922694.xlsx
@@ -131,7 +131,8 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Distributed Energy Resources Facilities by Year Opened - Dublin</a:t>
+              <a:t>Distributed Energy Resources Facilities by Year Opened -
+Dublin</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -167,10 +168,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -245,16 +246,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$26</c:f>
+              <c:f>Sheet1!$B$2:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -283,10 +287,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -361,16 +365,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$26</c:f>
+              <c:f>Sheet1!$C$2:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="22">
                   <c:v>1</c:v>
                 </c:pt>
@@ -378,6 +385,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
@@ -408,10 +418,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -486,16 +496,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$26</c:f>
+              <c:f>Sheet1!$D$2:$D$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
@@ -527,10 +540,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -605,16 +618,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$26</c:f>
+              <c:f>Sheet1!$E$2:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
@@ -656,6 +672,9 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -685,10 +704,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -763,16 +782,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$26</c:f>
+              <c:f>Sheet1!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -801,10 +823,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$A$2:$A$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -879,16 +901,19 @@
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$26</c:f>
+              <c:f>Sheet1!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1296,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -1510,6 +1535,17 @@
         <v>33</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
